--- a/data/inputs/trabajadores.xlsx
+++ b/data/inputs/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718B0742-88D6-7547-A06A-A3826AB3158E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80033505-91EE-2C4C-918E-C107D2F195F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18000" yWindow="660" windowWidth="11400" windowHeight="17140" xr2:uid="{93ADCB3C-DA1B-7146-A2FE-0804F0036F5D}"/>
   </bookViews>
@@ -1235,7 +1235,7 @@
         <v>36</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1252,7 +1252,7 @@
         <v>37</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -1269,7 +1269,7 @@
         <v>38</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1286,7 +1286,7 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1303,7 +1303,7 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>42</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -1354,7 +1354,7 @@
         <v>43</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -1371,7 +1371,7 @@
         <v>44</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -1388,7 +1388,7 @@
         <v>45</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -1405,7 +1405,7 @@
         <v>40</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>41</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>1</v>

--- a/data/inputs/trabajadores.xlsx
+++ b/data/inputs/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80033505-91EE-2C4C-918E-C107D2F195F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7087BC31-9EFF-A946-BC76-85EB02171240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18000" yWindow="660" windowWidth="11400" windowHeight="17140" xr2:uid="{93ADCB3C-DA1B-7146-A2FE-0804F0036F5D}"/>
   </bookViews>

--- a/data/inputs/trabajadores.xlsx
+++ b/data/inputs/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7087BC31-9EFF-A946-BC76-85EB02171240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE707020-2150-B74C-A47C-3C3B785A061D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18000" yWindow="660" windowWidth="11400" windowHeight="17140" xr2:uid="{93ADCB3C-DA1B-7146-A2FE-0804F0036F5D}"/>
   </bookViews>
@@ -1235,7 +1235,7 @@
         <v>36</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1252,7 +1252,7 @@
         <v>37</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -1269,7 +1269,7 @@
         <v>38</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1286,7 +1286,7 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1303,7 +1303,7 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>42</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -1354,7 +1354,7 @@
         <v>43</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -1371,7 +1371,7 @@
         <v>44</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -1388,7 +1388,7 @@
         <v>45</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -1405,7 +1405,7 @@
         <v>40</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>41</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>1</v>

--- a/data/inputs/trabajadores.xlsx
+++ b/data/inputs/trabajadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE707020-2150-B74C-A47C-3C3B785A061D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E175262-A4F1-E54A-B242-11D2A118773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18000" yWindow="660" windowWidth="11400" windowHeight="17140" xr2:uid="{93ADCB3C-DA1B-7146-A2FE-0804F0036F5D}"/>
+    <workbookView xWindow="3900" yWindow="660" windowWidth="25500" windowHeight="17140" xr2:uid="{93ADCB3C-DA1B-7146-A2FE-0804F0036F5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -146,18 +146,6 @@
     <t>cierre</t>
   </si>
   <si>
-    <t>T1_AbreCierra</t>
-  </si>
-  <si>
-    <t>T2_AbreCierra</t>
-  </si>
-  <si>
-    <t>T3_AbreCierra</t>
-  </si>
-  <si>
-    <t>T4_Cierra</t>
-  </si>
-  <si>
     <t>T5</t>
   </si>
   <si>
@@ -177,6 +165,21 @@
   </si>
   <si>
     <t>T7</t>
+  </si>
+  <si>
+    <t>T8</t>
+  </si>
+  <si>
+    <t>T9</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>T12</t>
   </si>
 </sst>
 </file>
@@ -557,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE69C77-60EA-3447-BDB6-4708F7AE5D89}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -1232,10 +1235,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -1249,10 +1252,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -1266,10 +1269,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1283,13 +1286,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1300,16 +1303,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -1317,16 +1320,16 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -1402,7 +1405,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1419,7 +1422,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -1429,23 +1432,6 @@
       </c>
       <c r="G42">
         <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43" t="s">
-        <v>46</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
